--- a/results/2026-04-07-SAT-precedence-graph/results_sat_scl_finsteps123_totalizer_prec_graph_120s.xlsx
+++ b/results/2026-04-07-SAT-precedence-graph/results_sat_scl_finsteps123_totalizer_prec_graph_120s.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="104">
   <si>
     <t>algorithm_time</t>
   </si>
@@ -367,6 +367,15 @@
   </si>
   <si>
     <t>stationB12</t>
+  </si>
+  <si>
+    <t>original average</t>
+  </si>
+  <si>
+    <t>track average</t>
+  </si>
+  <si>
+    <t>station average</t>
   </si>
 </sst>
 </file>
@@ -382,15 +391,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -398,12 +413,29 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -688,7 +720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z73"/>
+  <dimension ref="A1:AD73"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
@@ -719,7 +751,7 @@
     <col min="26" max="26" width="3.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -798,8 +830,17 @@
       <c r="Z1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AB1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0.64066139</v>
       </c>
@@ -878,8 +919,20 @@
       <c r="Z2">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AB2" s="2">
+        <f>AVERAGE(R2:R25)</f>
+        <v>46.81205679166667</v>
+      </c>
+      <c r="AC2" s="2">
+        <f>AVERAGE(R26:R49)</f>
+        <v>33.508532500000001</v>
+      </c>
+      <c r="AD2" s="2">
+        <f>AVERAGE(R50:R73)</f>
+        <v>45.522758791666668</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1.5076574999999899E-2</v>
       </c>
@@ -959,7 +1012,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1.6829588999999999E-2</v>
       </c>
@@ -1039,7 +1092,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1.4783773E-2</v>
       </c>
@@ -1119,7 +1172,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1.4923281E-2</v>
       </c>
@@ -1199,7 +1252,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1.3025046E-2</v>
       </c>
@@ -1279,7 +1332,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1.1400627E-2</v>
       </c>
@@ -1359,7 +1412,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2.3558503000000001E-2</v>
       </c>
@@ -1439,7 +1492,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1.1787206999999999E-2</v>
       </c>
@@ -1519,7 +1572,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>1.6963850999999999E-2</v>
       </c>
@@ -1599,7 +1652,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>3.2810461999999999E-2</v>
       </c>
@@ -1679,7 +1732,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>3.2953510999999998E-2</v>
       </c>
@@ -1759,7 +1812,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>1.1349282E-2</v>
       </c>
@@ -1839,7 +1892,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>1.1994458E-2</v>
       </c>
@@ -1919,7 +1972,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>1.2339378E-2</v>
       </c>
